--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1431214-26-CM25</t>
+          <t>3904-66-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4229.26</v>
+        <v>20856.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1233616-18346-CM25</t>
+          <t>3904-1208-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>53754.68</v>
+        <v>2114.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2467-4756-CM25</t>
+          <t>1431214-26-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>MUNICIPALIDAD DE QUILLÓN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4561.57</v>
+        <v>4229.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1036569-232-CM25</t>
+          <t>1233616-18346-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1304.43</v>
+        <v>53754.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3671-1-CM26</t>
+          <t>2467-4756-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>27778.17</v>
+        <v>4561.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3904-79-CM26</t>
+          <t>1036569-232-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>Gobierno Regional de Ñuble</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>27844.69</v>
+        <v>1304.43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4252-84-CM26</t>
+          <t>3671-1-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9491.18</v>
+        <v>27778.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4256-78-CM26</t>
+          <t>3904-79-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2661.08</v>
+        <v>27844.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4519-117-CM26</t>
+          <t>4252-84-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.250.600-6</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7388.59</v>
+        <v>9491.18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057508-1515-CM26</t>
+          <t>4256-78-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1999.2</v>
+        <v>2661.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3497-158-CM26</t>
+          <t>4519-117-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.250.600-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7500.11</v>
+        <v>7388.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3904-282-CM26</t>
+          <t>1057508-1515-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3170.16</v>
+        <v>1999.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3497-231-CM26</t>
+          <t>3497-158-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1056.72</v>
+        <v>7500.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1233616-932-CM26</t>
+          <t>3904-282-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12195.12</v>
+        <v>3170.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1393-250-CM26</t>
+          <t>3497-231-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>1056.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>229-384-CM26</t>
+          <t>1233616-932-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10338.72</v>
+        <v>12195.12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1426096-17-CM26</t>
+          <t>1393-250-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1701.7</v>
+        <v>8255.860000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2727-551-CM26</t>
+          <t>229-384-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>7096.21</v>
+        <v>10338.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3659-566-CM26</t>
+          <t>1426096-17-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1031.66</v>
+        <v>1701.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057898-83-CM26</t>
+          <t>2727-551-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>15212.96</v>
+        <v>7096.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1036569-100-CM26</t>
+          <t>3659-566-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>32309.57</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2724-595-CM26</t>
+          <t>1057898-83-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,6 +1850,128 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
+        <v>15212.96</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1036569-100-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>62.000.390-5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Ñuble</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>32309.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2724-595-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
         <v>35481.04</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,12 +514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3904-66-CM25</t>
+          <t>3879-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>20856.82</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3904-1208-CM25</t>
+          <t>3659-1-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2114.75</v>
+        <v>31669.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1431214-26-CM25</t>
+          <t>3904-66-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4229.26</v>
+        <v>20856.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1233616-18346-CM25</t>
+          <t>229-128-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>53754.68</v>
+        <v>809.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2467-4756-CM25</t>
+          <t>4252-96-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4561.57</v>
+        <v>8611.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1036569-232-CM25</t>
+          <t>4256-83-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1304.43</v>
+        <v>1775.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3671-1-CM26</t>
+          <t>4364-111-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>27778.17</v>
+        <v>856.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3904-79-CM26</t>
+          <t>3904-399-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>27844.69</v>
+        <v>1480.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4252-84-CM26</t>
+          <t>1393-185-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9491.18</v>
+        <v>5770.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4256-78-CM26</t>
+          <t>1036569-120-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2661.08</v>
+        <v>28344.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4519-117-CM26</t>
+          <t>229-369-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.250.600-6</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7388.59</v>
+        <v>11959.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057508-1515-CM26</t>
+          <t>2724-1194-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1999.2</v>
+        <v>35509.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3497-158-CM26</t>
+          <t>3904-1208-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7500.11</v>
+        <v>2114.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3904-282-CM26</t>
+          <t>4174-454-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3170.16</v>
+        <v>3104.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3497-231-CM26</t>
+          <t>1431214-26-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>MUNICIPALIDAD DE QUILLÓN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1056.72</v>
+        <v>4229.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1233616-932-CM26</t>
+          <t>1233616-18346-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12195.12</v>
+        <v>53754.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1393-250-CM26</t>
+          <t>2467-4756-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>4561.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>229-384-CM26</t>
+          <t>1036569-232-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>Gobierno Regional de Ñuble</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10338.72</v>
+        <v>1304.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1426096-17-CM26</t>
+          <t>3671-1-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1701.7</v>
+        <v>27778.17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2727-551-CM26</t>
+          <t>3904-79-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7096.21</v>
+        <v>27844.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3659-566-CM26</t>
+          <t>4252-84-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1031.66</v>
+        <v>9491.18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057898-83-CM26</t>
+          <t>4256-78-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>15212.96</v>
+        <v>2661.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1036569-100-CM26</t>
+          <t>4519-117-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.250.600-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>32309.57</v>
+        <v>7388.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2724-595-CM26</t>
+          <t>1057508-1515-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,7 +1972,861 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
+        <v>1999.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3497-158-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.140.400-5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>7500.11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3904-282-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.141.200-8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE BULNES</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>3170.16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3497-231-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.140.400-5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1056.72</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1233616-932-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>NETSUS SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>12195.12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1393-250-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>8255.860000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>229-384-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.141.100-1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>10338.72</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1426096-17-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Site Chile Sociedad Anónima</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>96.988.790-8</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>1701.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2727-551-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>7096.21</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3659-566-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>1031.66</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1057898-83-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.607.000-2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD NUBLE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>15212.96</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1036569-100-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>62.000.390-5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Ñuble</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>32309.57</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2724-595-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
         <v>35481.04</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1375761-1560-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.981.330-8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>12757.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1057508-2275-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.607.000-2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD NUBLE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>827.24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
@@ -636,7 +636,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3904-66-CM25</t>
+          <t>229-128-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ene-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>20856.82</v>
+        <v>809.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>229-128-CM25</t>
+          <t>4252-96-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>809.2</v>
+        <v>8611.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4252-96-CM25</t>
+          <t>4256-83-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8611.08</v>
+        <v>1775.48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4256-83-CM25</t>
+          <t>4364-111-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1775.48</v>
+        <v>856.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4364-111-CM25</t>
+          <t>3904-399-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>856.66</v>
+        <v>1480.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3904-399-CM25</t>
+          <t>1393-185-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1480.57</v>
+        <v>5770.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1393-185-CM25</t>
+          <t>1036569-120-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5770.31</v>
+        <v>28344.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1036569-120-CM25</t>
+          <t>229-369-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>28344.94</v>
+        <v>11959.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>229-369-CM25</t>
+          <t>2724-1194-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11959.5</v>
+        <v>35509.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2724-1194-CM25</t>
+          <t>3904-1208-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>35509.6</v>
+        <v>2114.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3904-1208-CM25</t>
+          <t>4174-454-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2114.75</v>
+        <v>3104.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4174-454-CM25</t>
+          <t>1431214-26-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3104.47</v>
+        <v>4229.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1431214-26-CM25</t>
+          <t>1233616-18346-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4229.26</v>
+        <v>53754.68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1233616-18346-CM25</t>
+          <t>2467-4756-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>53754.68</v>
+        <v>4561.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2467-4756-CM25</t>
+          <t>1036569-232-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4561.57</v>
+        <v>1304.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1036569-232-CM25</t>
+          <t>3671-1-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1304.43</v>
+        <v>27778.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3671-1-CM26</t>
+          <t>3904-79-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27778.17</v>
+        <v>27844.69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3904-79-CM26</t>
+          <t>4252-84-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>27844.69</v>
+        <v>9491.18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4252-84-CM26</t>
+          <t>4256-78-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9491.18</v>
+        <v>2661.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4256-78-CM26</t>
+          <t>4519-117-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.250.600-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2661.08</v>
+        <v>7388.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4519-117-CM26</t>
+          <t>1057508-1515-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.250.600-6</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7388.59</v>
+        <v>1999.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057508-1515-CM26</t>
+          <t>3497-158-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1999.2</v>
+        <v>7500.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3497-158-CM26</t>
+          <t>3904-282-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7500.11</v>
+        <v>3170.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3904-282-CM26</t>
+          <t>3497-231-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3170.16</v>
+        <v>1056.72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3497-231-CM26</t>
+          <t>1233616-932-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1056.72</v>
+        <v>12195.12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1233616-932-CM26</t>
+          <t>1393-250-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>12195.12</v>
+        <v>8255.860000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1393-250-CM26</t>
+          <t>229-384-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>10338.72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>229-384-CM26</t>
+          <t>1426096-17-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10338.72</v>
+        <v>1701.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1426096-17-CM26</t>
+          <t>2727-551-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,22 +2359,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1701.7</v>
+        <v>7096.21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2727-551-CM26</t>
+          <t>3659-566-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7096.21</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3659-566-CM26</t>
+          <t>1057898-83-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1031.66</v>
+        <v>15212.96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057898-83-CM26</t>
+          <t>1036569-100-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>15212.96</v>
+        <v>32309.57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1036569-100-CM26</t>
+          <t>2724-595-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,22 +2603,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>32309.57</v>
+        <v>35481.04</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2724-595-CM26</t>
+          <t>1375761-1560-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>35481.04</v>
+        <v>12757.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1375761-1560-CM26</t>
+          <t>1057508-2275-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>12757.4</v>
+        <v>827.24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057508-2275-CM26</t>
+          <t>3674-585-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>827.24</v>
+        <v>17577.25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
@@ -562,7 +562,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2053,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2118,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2183,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2248,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2313,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2378,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2504,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2569,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2634,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2699,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2764,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2829,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2894,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2959,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2521,7 +2521,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3659-566-CM26</t>
+          <t>1057898-83-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2541,17 +2541,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1031.66</v>
+        <v>15212.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1057898-83-CM26</t>
+          <t>3659-566-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2626,17 +2626,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>15212.96</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="35">
@@ -2971,6 +2971,136 @@
       </c>
       <c r="M39" s="2" t="n">
         <v>17577.25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4121-82-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>1079.57</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1233616-1906-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>46131.54</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -644,7 +644,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>229-128-CM25</t>
+          <t>3904-66-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>809.2</v>
+        <v>20856.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4252-96-CM25</t>
+          <t>229-128-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -768,13 +768,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8611.08</v>
+        <v>809.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4256-83-CM25</t>
+          <t>4252-96-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1775.48</v>
+        <v>8611.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4364-111-CM25</t>
+          <t>4256-83-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -898,13 +898,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>856.66</v>
+        <v>1775.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3904-399-CM25</t>
+          <t>4364-111-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1480.57</v>
+        <v>856.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1393-185-CM25</t>
+          <t>3904-399-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5770.31</v>
+        <v>1480.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1036569-120-CM25</t>
+          <t>1393-185-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,22 +1049,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>28344.94</v>
+        <v>5770.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>229-369-CM25</t>
+          <t>1036569-120-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,27 +1109,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>11959.5</v>
+        <v>28344.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2724-1194-CM25</t>
+          <t>229-369-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,27 +1174,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35509.6</v>
+        <v>11959.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3904-1208-CM25</t>
+          <t>2724-1194-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1239,27 +1239,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2114.75</v>
+        <v>35509.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4174-454-CM25</t>
+          <t>3904-1208-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3104.47</v>
+        <v>2114.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1431214-26-CM25</t>
+          <t>4174-454-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4229.26</v>
+        <v>3104.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1233616-18346-CM25</t>
+          <t>1431214-26-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1439,22 +1439,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>53754.68</v>
+        <v>4229.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2467-4756-CM25</t>
+          <t>1233616-18346-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,27 +1499,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4561.57</v>
+        <v>53754.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1036569-232-CM25</t>
+          <t>2467-4756-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1304.43</v>
+        <v>4561.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3671-1-CM26</t>
+          <t>1036569-232-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,12 +1629,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>27778.17</v>
+        <v>1304.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3904-79-CM26</t>
+          <t>3671-1-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27844.69</v>
+        <v>27778.17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4252-84-CM26</t>
+          <t>3904-79-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9491.18</v>
+        <v>27844.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4256-78-CM26</t>
+          <t>4252-84-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2661.08</v>
+        <v>9491.18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4519-117-CM26</t>
+          <t>4256-78-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.250.600-6</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7388.59</v>
+        <v>2661.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057508-1515-CM26</t>
+          <t>4519-117-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,27 +1954,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.250.600-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1984,28 +1984,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1999.2</v>
+        <v>7388.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3497-158-CM26</t>
+          <t>1057508-1515-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2020,7 +2024,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2030,12 +2034,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2045,32 +2049,28 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7500.11</v>
+        <v>1999.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3904-282-CM26</t>
+          <t>3497-158-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2085,22 +2085,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2110,17 +2110,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3170.16</v>
+        <v>7500.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3497-231-CM26</t>
+          <t>3904-282-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2145,27 +2145,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2175,17 +2175,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2194,13 +2194,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1056.72</v>
+        <v>3170.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1233616-932-CM26</t>
+          <t>3497-231-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>12195.12</v>
+        <v>1056.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1393-250-CM26</t>
+          <t>1233616-932-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2280,22 +2280,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>12195.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>229-384-CM26</t>
+          <t>1393-250-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10338.72</v>
+        <v>8255.860000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1426096-17-CM26</t>
+          <t>229-384-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2435,28 +2435,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1701.7</v>
+        <v>10338.72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2727-551-CM26</t>
+          <t>1426096-17-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2471,7 +2475,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2481,12 +2485,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2496,32 +2500,28 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.988.790-8</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7096.21</v>
+        <v>1701.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057898-83-CM26</t>
+          <t>2727-551-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15212.96</v>
+        <v>7096.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3659-566-CM26</t>
+          <t>1057898-83-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2626,17 +2626,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1031.66</v>
+        <v>15212.96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1036569-100-CM26</t>
+          <t>3659-566-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2710,13 +2710,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>32309.57</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2724-595-CM26</t>
+          <t>1036569-100-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>35481.04</v>
+        <v>32309.57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1375761-1560-CM26</t>
+          <t>2724-595-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2840,13 +2840,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12757.4</v>
+        <v>35481.04</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1057508-2275-CM26</t>
+          <t>1375761-1560-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2905,13 +2905,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>827.24</v>
+        <v>12757.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3674-585-CM26</t>
+          <t>1057508-2275-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2921,27 +2921,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2970,13 +2970,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>17577.25</v>
+        <v>827.24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4121-82-CM26</t>
+          <t>3674-585-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3035,71 +3035,136 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1079.57</v>
+        <v>17577.25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>4121-82-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>1079.57</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>1233616-1906-CM26</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>61.980.940-8</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
         <v>46131.54</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2586,7 +2586,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1057898-83-CM26</t>
+          <t>3659-566-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2626,17 +2626,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>15212.96</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3659-566-CM26</t>
+          <t>1057898-83-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1031.66</v>
+        <v>15212.96</v>
       </c>
     </row>
     <row r="36">
@@ -3166,6 +3166,67 @@
       </c>
       <c r="M42" s="2" t="n">
         <v>46131.54</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3904-1167-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.141.200-8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE BULNES</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>NextTime Software S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>99.576.370-2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>2627.52</v>
       </c>
     </row>
   </sheetData>
